--- a/AAAGameData/DataTables/Level/LevelTagTable.xlsx
+++ b/AAAGameData/DataTables/Level/LevelTagTable.xlsx
@@ -3083,67 +3083,6 @@
       <c r="X33" s="1" t="n"/>
       <c r="Y33" s="1" t="n"/>
     </row>
-    <row r="34" ht="56.75" customHeight="1" s="2">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>技术攻坚</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>每个科研建筑可以额外研发{0}项科技，但所有科技的研发价格+{1}</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="n"/>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_TechBreakthrough</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>UI/LvTag/TechBreakthrough</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_Name_TechBreakthrough</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_Desc_TechBreakthrough</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="n"/>
-      <c r="L34" s="1" t="n"/>
-      <c r="M34" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N34" s="1" t="n"/>
-      <c r="O34" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="P34" s="1" t="n"/>
-      <c r="Q34" s="1" t="n"/>
-      <c r="R34" s="1" t="n"/>
-      <c r="S34" s="1" t="n"/>
-      <c r="T34" s="1" t="n"/>
-      <c r="U34" s="1" t="n"/>
-      <c r="V34" s="1" t="n"/>
-      <c r="W34" s="1" t="n"/>
-      <c r="X34" s="1" t="n"/>
-      <c r="Y34" s="1" t="n"/>
-    </row>
     <row r="35" ht="70.75" customHeight="1" s="2">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="n">
@@ -4692,132 +4631,6 @@
       <c r="W59" s="1" t="n"/>
       <c r="X59" s="1" t="n"/>
       <c r="Y59" s="1" t="n"/>
-    </row>
-    <row r="60" ht="28.75" customHeight="1" s="2">
-      <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>技术封锁I</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>科研建筑研发科技的价格+{0}橙髓</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_TechEmbargoI</t>
-        </is>
-      </c>
-      <c r="H60" s="1" t="inlineStr">
-        <is>
-          <t>UI/LvTag/TechEmbargoI</t>
-        </is>
-      </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_Name_TechEmbargoI</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_Desc_TechEmbargoI</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="n"/>
-      <c r="L60" s="1" t="n"/>
-      <c r="M60" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" s="1" t="n"/>
-      <c r="Q60" s="1" t="n"/>
-      <c r="R60" s="1" t="n"/>
-      <c r="S60" s="1" t="n"/>
-      <c r="T60" s="1" t="n"/>
-      <c r="U60" s="1" t="n"/>
-      <c r="V60" s="1" t="n"/>
-      <c r="W60" s="1" t="n"/>
-      <c r="X60" s="1" t="n"/>
-      <c r="Y60" s="1" t="n"/>
-    </row>
-    <row r="61" ht="28.75" customHeight="1" s="2">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>技术封锁II</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>科研建筑研发科技的价格+{0}橙髓</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_TechEmbargoII</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="inlineStr">
-        <is>
-          <t>UI/LvTag/TechEmbargoII</t>
-        </is>
-      </c>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_Name_TechEmbargoII</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>LvTag_Desc_TechEmbargoII</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="n"/>
-      <c r="L61" s="1" t="n"/>
-      <c r="M61" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N61" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="1" t="n"/>
-      <c r="Q61" s="1" t="n"/>
-      <c r="R61" s="1" t="n"/>
-      <c r="S61" s="1" t="n"/>
-      <c r="T61" s="1" t="n"/>
-      <c r="U61" s="1" t="n"/>
-      <c r="V61" s="1" t="n"/>
-      <c r="W61" s="1" t="n"/>
-      <c r="X61" s="1" t="n"/>
-      <c r="Y61" s="1" t="n"/>
     </row>
     <row r="62" ht="28.75" customHeight="1" s="2">
       <c r="A62" s="1" t="n"/>

--- a/AAAGameData/DataTables/Level/LevelTagTable.xlsx
+++ b/AAAGameData/DataTables/Level/LevelTagTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
   <si>
     <t>#</t>
   </si>
@@ -718,24 +718,6 @@
   </si>
   <si>
     <t>LvTag_Desc_ForceReduction</t>
-  </si>
-  <si>
-    <t>严密布控</t>
-  </si>
-  <si>
-    <t>敌方建筑阻止单位部署的范围扩大{0}%</t>
-  </si>
-  <si>
-    <t>LvTag_TightSecurity</t>
-  </si>
-  <si>
-    <t>UI/LvTag/TightSecurity</t>
-  </si>
-  <si>
-    <t>LvTag_Name_TightSecurity</t>
-  </si>
-  <si>
-    <t>LvTag_Desc_TightSecurity</t>
   </si>
   <si>
     <t>补给匮乏</t>
@@ -2881,7 +2863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y130"/>
+  <dimension ref="A1:Y129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1" style="2"/>
@@ -4554,10 +4536,10 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" ht="42.75" customHeight="1" s="2" customFormat="1">
+    <row r="37" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>235</v>
@@ -4566,7 +4548,7 @@
         <v>236</v>
       </c>
       <c r="E37" s="1">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
@@ -4603,10 +4585,10 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" ht="28.75" customHeight="1" s="2" customFormat="1">
+    <row r="38" ht="42.75" customHeight="1" s="2" customFormat="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>241</v>
@@ -4652,10 +4634,10 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" ht="42.75" customHeight="1" s="2" customFormat="1">
+    <row r="39" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>247</v>
@@ -4664,7 +4646,7 @@
         <v>248</v>
       </c>
       <c r="E39" s="1">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
@@ -4701,10 +4683,10 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40" ht="28.75" customHeight="1" s="2" customFormat="1">
+    <row r="40" ht="42.75" customHeight="1" s="2" customFormat="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>253</v>
@@ -4713,7 +4695,7 @@
         <v>254</v>
       </c>
       <c r="E40" s="1">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
@@ -4750,10 +4732,10 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41" ht="42.75" customHeight="1" s="2" customFormat="1">
+    <row r="41" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>259</v>
@@ -4761,21 +4743,21 @@
       <c r="D41" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E41" s="1">
-        <v>100</v>
+      <c r="E41" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -4802,16 +4784,16 @@
     <row r="42" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E42" s="1" t="s">
         <v>267</v>
+      </c>
+      <c r="E42" s="1">
+        <v>70</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
@@ -4851,7 +4833,7 @@
     <row r="43" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>272</v>
@@ -4860,7 +4842,7 @@
         <v>273</v>
       </c>
       <c r="E43" s="1">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
@@ -4900,7 +4882,7 @@
     <row r="44" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>278</v>
@@ -4909,7 +4891,7 @@
         <v>279</v>
       </c>
       <c r="E44" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
@@ -4949,7 +4931,7 @@
     <row r="45" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>284</v>
@@ -4958,7 +4940,7 @@
         <v>285</v>
       </c>
       <c r="E45" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
@@ -4998,7 +4980,7 @@
     <row r="46" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>290</v>
@@ -5007,9 +4989,11 @@
         <v>291</v>
       </c>
       <c r="E46" s="1">
-        <v>40</v>
-      </c>
-      <c r="F46" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
       <c r="G46" s="1" t="s">
         <v>292</v>
       </c>
@@ -5047,31 +5031,31 @@
     <row r="47" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E47" s="1">
+        <v>7</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E47" s="1">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="J47" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -5079,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O47" s="1">
         <v>1</v>
@@ -5098,31 +5082,31 @@
     <row r="48" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E48" s="1">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E48" s="1">
-        <v>7</v>
-      </c>
-      <c r="F48" s="1">
-        <v>1</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -5130,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O48" s="1">
         <v>1</v>
@@ -5149,19 +5133,19 @@
     <row r="49" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E49" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>308</v>
@@ -5181,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O49" s="1">
         <v>1</v>
@@ -5200,31 +5184,31 @@
     <row r="50" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>312</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="1">
         <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="J50" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -5232,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="1">
         <v>1</v>
@@ -5251,31 +5235,31 @@
     <row r="51" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="1">
         <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="J51" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -5283,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -5302,19 +5286,19 @@
     <row r="52" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E52" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>324</v>
@@ -5334,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O52" s="1">
         <v>1</v>
@@ -5353,7 +5337,7 @@
     <row r="53" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>328</v>
@@ -5385,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" s="1">
         <v>1</v>
@@ -5404,7 +5388,7 @@
     <row r="54" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>334</v>
@@ -5436,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O54" s="1">
         <v>1</v>
@@ -5452,85 +5436,85 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" ht="28.75" customHeight="1" s="2" customFormat="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1">
-        <v>55</v>
-      </c>
-      <c r="C55" s="1" t="s">
+    <row r="57" ht="28.75" customHeight="1" s="2" customFormat="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1">
+        <v>58</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
-      <c r="F55" s="1">
-        <v>4</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1">
+        <v>6</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1" t="b">
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N55" s="1">
-        <v>3</v>
-      </c>
-      <c r="O55" s="1">
-        <v>1</v>
-      </c>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
+      <c r="N57" s="1">
+        <v>1</v>
+      </c>
+      <c r="O57" s="1">
+        <v>1</v>
+      </c>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
     </row>
     <row r="58" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>346</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E58" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58" s="1">
         <v>6</v>
       </c>
       <c r="G58" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -5538,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="1">
         <v>1</v>
@@ -5557,31 +5541,31 @@
     <row r="59" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E59" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F59" s="1">
         <v>6</v>
       </c>
       <c r="G59" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="I59" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -5589,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O59" s="1">
         <v>1</v>
@@ -5608,19 +5592,19 @@
     <row r="60" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="E60" s="1">
+        <v>30</v>
+      </c>
+      <c r="F60" s="1">
         <v>7</v>
-      </c>
-      <c r="F60" s="1">
-        <v>6</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>358</v>
@@ -5640,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -5659,31 +5643,31 @@
     <row r="61" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>362</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E61" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F61" s="1">
         <v>7</v>
       </c>
       <c r="G61" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="J61" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -5691,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" s="1">
         <v>1</v>
@@ -5710,31 +5694,31 @@
     <row r="62" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E62" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1">
         <v>7</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -5742,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O62" s="1">
         <v>1</v>
@@ -5761,19 +5745,19 @@
     <row r="63" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="E63" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F63" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>374</v>
@@ -5793,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O63" s="1">
         <v>1</v>
@@ -5812,31 +5796,31 @@
     <row r="64" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>378</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E64" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F64" s="1">
         <v>8</v>
       </c>
       <c r="G64" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="I64" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -5844,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O64" s="1">
         <v>1</v>
@@ -5863,31 +5847,31 @@
     <row r="65" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E65" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F65" s="1">
         <v>8</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -5895,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O65" s="1">
         <v>1</v>
@@ -5914,20 +5898,18 @@
     <row r="66" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E66" s="1">
-        <v>60</v>
-      </c>
-      <c r="F66" s="1">
-        <v>8</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
         <v>390</v>
       </c>
@@ -5946,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O66" s="1">
         <v>1</v>
@@ -5965,7 +5947,7 @@
     <row r="67" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>394</v>
@@ -5974,7 +5956,7 @@
         <v>395</v>
       </c>
       <c r="E67" s="1">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
@@ -6014,7 +5996,7 @@
     <row r="68" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>400</v>
@@ -6023,9 +6005,11 @@
         <v>401</v>
       </c>
       <c r="E68" s="1">
-        <v>3</v>
-      </c>
-      <c r="F68" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="F68" s="1">
+        <v>9</v>
+      </c>
       <c r="G68" s="1" t="s">
         <v>402</v>
       </c>
@@ -6063,31 +6047,31 @@
     <row r="69" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>406</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E69" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F69" s="1">
         <v>9</v>
       </c>
       <c r="G69" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -6095,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69" s="1">
         <v>1</v>
@@ -6114,31 +6098,31 @@
     <row r="70" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E70" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F70" s="1">
         <v>9</v>
       </c>
       <c r="G70" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -6146,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O70" s="1">
         <v>1</v>
@@ -6165,19 +6149,19 @@
     <row r="71" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E71" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F71" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>418</v>
@@ -6197,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O71" s="1">
         <v>1</v>
@@ -6216,31 +6200,31 @@
     <row r="72" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>422</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E72" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F72" s="1">
         <v>10</v>
       </c>
       <c r="G72" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="I72" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -6248,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" s="1">
         <v>1</v>
@@ -6267,31 +6251,29 @@
     <row r="73" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E73" s="1">
+        <v>60</v>
+      </c>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E73" s="1">
-        <v>45</v>
-      </c>
-      <c r="F73" s="1">
-        <v>10</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="H73" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -6299,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="N73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" s="1">
         <v>1</v>
@@ -6318,16 +6300,16 @@
     <row r="74" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E74" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
@@ -6367,7 +6349,7 @@
     <row r="75" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>438</v>
@@ -6376,7 +6358,7 @@
         <v>439</v>
       </c>
       <c r="E75" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
@@ -6416,7 +6398,7 @@
     <row r="76" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>444</v>
@@ -6425,7 +6407,7 @@
         <v>445</v>
       </c>
       <c r="E76" s="1">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
@@ -6465,7 +6447,7 @@
     <row r="77" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>450</v>
@@ -6474,7 +6456,7 @@
         <v>451</v>
       </c>
       <c r="E77" s="1">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
@@ -6514,7 +6496,7 @@
     <row r="78" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>456</v>
@@ -6523,9 +6505,11 @@
         <v>457</v>
       </c>
       <c r="E78" s="1">
-        <v>3</v>
-      </c>
-      <c r="F78" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="F78" s="1">
+        <v>11</v>
+      </c>
       <c r="G78" s="1" t="s">
         <v>458</v>
       </c>
@@ -6563,31 +6547,31 @@
     <row r="79" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>462</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E79" s="1">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F79" s="1">
         <v>11</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -6595,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O79" s="1">
         <v>1</v>
@@ -6614,19 +6598,19 @@
     <row r="80" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C80" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="E80" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F80" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>469</v>
@@ -6646,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="N80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O80" s="1">
         <v>1</v>
@@ -6665,31 +6649,31 @@
     <row r="81" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>473</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E81" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F81" s="1">
         <v>12</v>
       </c>
       <c r="G81" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="H81" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="J81" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -6697,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O81" s="1">
         <v>1</v>
@@ -6716,31 +6700,31 @@
     <row r="82" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E82" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F82" s="1">
         <v>12</v>
       </c>
       <c r="G82" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="J82" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -6748,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" s="1">
         <v>1</v>
@@ -6767,20 +6751,18 @@
     <row r="83" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E83" s="1">
-        <v>120</v>
-      </c>
-      <c r="F83" s="1">
-        <v>12</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
         <v>485</v>
       </c>
@@ -6799,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O83" s="1">
         <v>1</v>
@@ -6818,7 +6800,7 @@
     <row r="84" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>489</v>
@@ -6827,9 +6809,11 @@
         <v>490</v>
       </c>
       <c r="E84" s="1">
-        <v>33</v>
-      </c>
-      <c r="F84" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="F84" s="1">
+        <v>13</v>
+      </c>
       <c r="G84" s="1" t="s">
         <v>491</v>
       </c>
@@ -6867,31 +6851,31 @@
     <row r="85" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>495</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E85" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F85" s="1">
         <v>13</v>
       </c>
       <c r="G85" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="J85" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -6899,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" s="1">
         <v>1</v>
@@ -6918,19 +6902,19 @@
     <row r="86" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="E86" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F86" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>502</v>
@@ -6950,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O86" s="1">
         <v>1</v>
@@ -6969,31 +6953,31 @@
     <row r="87" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>506</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E87" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F87" s="1">
         <v>14</v>
       </c>
       <c r="G87" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="J87" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -7001,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" s="1">
         <v>1</v>
@@ -7020,31 +7004,31 @@
     <row r="88" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E88" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F88" s="1">
         <v>14</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
@@ -7052,7 +7036,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O88" s="1">
         <v>1</v>
@@ -7071,20 +7055,18 @@
     <row r="89" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="E89" s="1">
-        <v>120</v>
-      </c>
-      <c r="F89" s="1">
-        <v>14</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
         <v>518</v>
       </c>
@@ -7103,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O89" s="1">
         <v>1</v>
@@ -7122,7 +7104,7 @@
     <row r="90" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>522</v>
@@ -7131,7 +7113,7 @@
         <v>523</v>
       </c>
       <c r="E90" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1" t="s">
@@ -7171,7 +7153,7 @@
     <row r="91" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>528</v>
@@ -7180,9 +7162,11 @@
         <v>529</v>
       </c>
       <c r="E91" s="1">
-        <v>60</v>
-      </c>
-      <c r="F91" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="F91" s="1">
+        <v>15</v>
+      </c>
       <c r="G91" s="1" t="s">
         <v>530</v>
       </c>
@@ -7220,31 +7204,31 @@
     <row r="92" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>534</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E92" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F92" s="1">
         <v>15</v>
       </c>
       <c r="G92" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="H92" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="I92" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="J92" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -7252,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O92" s="1">
         <v>1</v>
@@ -7271,19 +7255,19 @@
     <row r="93" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="E93" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F93" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>541</v>
@@ -7303,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O93" s="1">
         <v>1</v>
@@ -7322,31 +7306,31 @@
     <row r="94" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>545</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E94" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F94" s="1">
         <v>16</v>
       </c>
       <c r="G94" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="I94" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="J94" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
@@ -7354,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O94" s="1">
         <v>1</v>
@@ -7373,19 +7357,19 @@
     <row r="95" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="E95" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F95" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>552</v>
@@ -7405,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O95" s="1">
         <v>1</v>
@@ -7424,31 +7408,31 @@
     <row r="96" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>556</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E96" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F96" s="1">
         <v>17</v>
       </c>
       <c r="G96" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H96" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="I96" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>561</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -7456,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96" s="1">
         <v>1</v>
@@ -7475,19 +7459,19 @@
     <row r="97" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="E97" s="1">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>563</v>
@@ -7507,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O97" s="1">
         <v>1</v>
@@ -7526,31 +7510,31 @@
     <row r="98" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>567</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E98" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1">
         <v>18</v>
       </c>
       <c r="G98" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="H98" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="J98" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -7558,7 +7542,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O98" s="1">
         <v>1</v>
@@ -7577,20 +7561,18 @@
     <row r="99" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C99" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="E99" s="1">
-        <v>8</v>
-      </c>
-      <c r="F99" s="1">
-        <v>18</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F99" s="1"/>
       <c r="G99" s="1" t="s">
         <v>574</v>
       </c>
@@ -7609,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O99" s="1">
         <v>1</v>
@@ -7628,7 +7610,7 @@
     <row r="100" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>578</v>
@@ -7637,9 +7619,11 @@
         <v>579</v>
       </c>
       <c r="E100" s="1">
-        <v>50</v>
-      </c>
-      <c r="F100" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="F100" s="1">
+        <v>19</v>
+      </c>
       <c r="G100" s="1" t="s">
         <v>580</v>
       </c>
@@ -7677,31 +7661,31 @@
     <row r="101" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>584</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E101" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F101" s="1">
         <v>19</v>
       </c>
       <c r="G101" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="I101" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="J101" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -7709,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O101" s="1">
         <v>1</v>
@@ -7728,20 +7712,18 @@
     <row r="102" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="E102" s="1">
         <v>40</v>
       </c>
-      <c r="F102" s="1">
-        <v>19</v>
-      </c>
+      <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
         <v>591</v>
       </c>
@@ -7760,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O102" s="1">
         <v>1</v>
@@ -7779,7 +7761,7 @@
     <row r="103" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>595</v>
@@ -7788,7 +7770,7 @@
         <v>596</v>
       </c>
       <c r="E103" s="1">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1" t="s">
@@ -7828,7 +7810,7 @@
     <row r="104" ht="28.75" customHeight="1" s="2" customFormat="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>601</v>
@@ -7837,7 +7819,7 @@
         <v>602</v>
       </c>
       <c r="E104" s="1">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
@@ -7874,44 +7856,22 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" ht="28.75" customHeight="1" s="2" customFormat="1">
+    <row r="105">
       <c r="A105" s="1"/>
-      <c r="B105" s="1">
-        <v>105</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>612</v>
-      </c>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
-      <c r="M105" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N105" s="1">
-        <v>1</v>
-      </c>
-      <c r="O105" s="1">
-        <v>1</v>
-      </c>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
@@ -7923,7 +7883,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" ht="14.75" customHeight="1" s="2" customFormat="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -8571,33 +8531,6 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" ht="14.75" customHeight="1" s="2" customFormat="1">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
-      <c r="K130" s="1"/>
-      <c r="L130" s="1"/>
-      <c r="M130" s="1"/>
-      <c r="N130" s="1"/>
-      <c r="O130" s="1"/>
-      <c r="P130" s="1"/>
-      <c r="Q130" s="1"/>
-      <c r="R130" s="1"/>
-      <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
-      <c r="U130" s="1"/>
-      <c r="V130" s="1"/>
-      <c r="W130" s="1"/>
-      <c r="X130" s="1"/>
-      <c r="Y130" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
